--- a/output_data/charts/crashSeverityByType-Pickaway.xlsx
+++ b/output_data/charts/crashSeverityByType-Pickaway.xlsx
@@ -40,12 +40,12 @@
     <t>Overturning</t>
   </si>
   <si>
+    <t>Pedestrian</t>
+  </si>
+  <si>
     <t>Rear End</t>
   </si>
   <si>
-    <t>Pedestrian</t>
-  </si>
-  <si>
     <t>Right Turn</t>
   </si>
   <si>
@@ -55,19 +55,19 @@
     <t>Left Turn</t>
   </si>
   <si>
+    <t>Other Non-Collision</t>
+  </si>
+  <si>
     <t>Parked Vehicle</t>
   </si>
   <si>
-    <t>Other Non-Collision</t>
-  </si>
-  <si>
     <t>Backing</t>
   </si>
   <si>
+    <t>Other Object</t>
+  </si>
+  <si>
     <t>Animal</t>
-  </si>
-  <si>
-    <t>Other Object</t>
   </si>
   <si>
     <t>Pedalcycles</t>
@@ -225,10 +225,10 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Pedestrian</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Right Turn</c:v>
@@ -240,19 +240,19 @@
                   <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>Pedalcycles</c:v>
@@ -273,37 +273,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>38.77551020408163</c:v>
+                  <c:v>36.53846153846153</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.20408163265306</c:v>
+                  <c:v>13.46153846153846</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.163265306122449</c:v>
+                  <c:v>11.53846153846154</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.163265306122449</c:v>
+                  <c:v>9.615384615384617</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.163265306122449</c:v>
+                  <c:v>7.692307692307693</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.163265306122449</c:v>
+                  <c:v>7.692307692307693</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.122448979591836</c:v>
+                  <c:v>3.846153846153846</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.081632653061225</c:v>
+                  <c:v>3.846153846153846</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.081632653061225</c:v>
+                  <c:v>1.923076923076923</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.040816326530612</c:v>
+                  <c:v>1.923076923076923</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.040816326530612</c:v>
+                  <c:v>1.923076923076923</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -367,10 +367,10 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Pedestrian</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Right Turn</c:v>
@@ -382,19 +382,19 @@
                   <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>Pedalcycles</c:v>
@@ -415,55 +415,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>32.51028806584362</c:v>
+                  <c:v>27.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.10699588477366</c:v>
+                  <c:v>18.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.407407407407407</c:v>
+                  <c:v>7.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.11522633744856</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10.2880658436214</c:v>
+                  <c:v>5.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.938271604938271</c:v>
+                  <c:v>9.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.411522633744856</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.11522633744856</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.938271604938271</c:v>
+                  <c:v>7.199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.11522633744856</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.349794238683128</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.05761316872428</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.411522633744856</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.234567901234568</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -509,10 +509,10 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Pedestrian</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Right Turn</c:v>
@@ -524,19 +524,19 @@
                   <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>Pedalcycles</c:v>
@@ -557,55 +557,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>22.21167536782155</c:v>
+                  <c:v>20.28962188254224</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.07087486157254</c:v>
+                  <c:v>12.9847144006436</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.96171491852555</c:v>
+                  <c:v>2.091713596138375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6453092865053</c:v>
+                  <c:v>1.882542236524537</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18.05094130675526</c:v>
+                  <c:v>0.7401448109412712</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.69609239044455</c:v>
+                  <c:v>17.58648431214803</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.1515582977377</c:v>
+                  <c:v>2.220434432823813</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.666192058218638</c:v>
+                  <c:v>9.718423169750604</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.600379686758425</c:v>
+                  <c:v>5.792437650844731</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.591203923429837</c:v>
+                  <c:v>4.15124698310539</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.828508147445025</c:v>
+                  <c:v>3.507642799678198</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.369719981015662</c:v>
+                  <c:v>3.218020917135962</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13.2890365448505</c:v>
+                  <c:v>0.6114239742558327</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6486315456415124</c:v>
+                  <c:v>14.25583266291231</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.221483942414175</c:v>
+                  <c:v>0.1448109412711183</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.0158202816010125</c:v>
+                  <c:v>0.01609010458567981</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.9808574592627749</c:v>
+                  <c:v>0.7884151246983104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1061,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>38.77551020408163</v>
+        <v>36.53846153846153</v>
       </c>
       <c r="C2" s="2">
-        <v>32.51028806584362</v>
+        <v>27.6</v>
       </c>
       <c r="D2" s="2">
-        <v>22.21167536782155</v>
+        <v>20.28962188254224</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>10.20408163265306</v>
+        <v>13.46153846153846</v>
       </c>
       <c r="C3" s="2">
-        <v>18.10699588477366</v>
+        <v>18.8</v>
       </c>
       <c r="D3" s="2">
-        <v>12.07087486157254</v>
+        <v>12.9847144006436</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>8.163265306122449</v>
+        <v>11.53846153846154</v>
       </c>
       <c r="C4" s="2">
-        <v>7.407407407407407</v>
+        <v>7.6</v>
       </c>
       <c r="D4" s="2">
-        <v>1.96171491852555</v>
+        <v>2.091713596138375</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1103,13 +1103,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>8.163265306122449</v>
+        <v>9.615384615384617</v>
       </c>
       <c r="C5" s="2">
-        <v>4.11522633744856</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2">
-        <v>1.6453092865053</v>
+        <v>1.882542236524537</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>8.163265306122449</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="C6" s="2">
-        <v>10.2880658436214</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="D6" s="2">
-        <v>18.05094130675526</v>
+        <v>0.7401448109412712</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>8.163265306122449</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="C7" s="2">
-        <v>4.938271604938271</v>
+        <v>9.6</v>
       </c>
       <c r="D7" s="2">
-        <v>0.69609239044455</v>
+        <v>17.58648431214803</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1145,13 +1145,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>6.122448979591836</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="C8" s="2">
-        <v>0.411522633744856</v>
+        <v>0.4</v>
       </c>
       <c r="D8" s="2">
-        <v>2.1515582977377</v>
+        <v>2.220434432823813</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1159,13 +1159,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>4.081632653061225</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="C9" s="2">
-        <v>4.11522633744856</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="2">
-        <v>9.666192058218638</v>
+        <v>9.718423169750604</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1173,13 +1173,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>4.081632653061225</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="C10" s="2">
-        <v>4.938271604938271</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D10" s="2">
-        <v>5.600379686758425</v>
+        <v>5.792437650844731</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1187,13 +1187,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>2.040816326530612</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="C11" s="2">
-        <v>4.11522633744856</v>
+        <v>6.4</v>
       </c>
       <c r="D11" s="2">
-        <v>3.591203923429837</v>
+        <v>4.15124698310539</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1201,13 +1201,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>2.040816326530612</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="C12" s="2">
-        <v>5.349794238683128</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="2">
-        <v>3.828508147445025</v>
+        <v>3.507642799678198</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2">
-        <v>3.369719981015662</v>
+        <v>3.218020917135962</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <v>2.05761316872428</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>13.2890365448505</v>
+        <v>0.6114239742558327</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>0.411522633744856</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="2">
-        <v>0.6486315456415124</v>
+        <v>14.25583266291231</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D16" s="2">
-        <v>0.221483942414175</v>
+        <v>0.1448109412711183</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>0.0158202816010125</v>
+        <v>0.01609010458567981</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1288,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>1.234567901234568</v>
+        <v>0.8</v>
       </c>
       <c r="D18" s="2">
-        <v>0.9808574592627749</v>
+        <v>0.7884151246983104</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Pickaway.xlsx
+++ b/output_data/charts/crashSeverityByType-Pickaway.xlsx
@@ -83,8 +83,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -141,7 +142,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -173,7 +174,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Pickaway County</a:t>
+              <a:t>Crash Severity by Type of Crash, Pickaway County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
